--- a/ExportExcel/Add Majors Test.xlsx
+++ b/ExportExcel/Add Majors Test.xlsx
@@ -41,7 +41,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>11389 ms</t>
+    <t>5441 ms</t>
   </si>
   <si>
     <t/>
@@ -53,7 +53,7 @@
     <t>TC_CM_02</t>
   </si>
   <si>
-    <t>6848 ms</t>
+    <t>6435 ms</t>
   </si>
   <si>
     <t>testAddMajorFailWithSpace</t>
@@ -62,7 +62,7 @@
     <t>TC_CM_03</t>
   </si>
   <si>
-    <t>5747 ms</t>
+    <t>4458 ms</t>
   </si>
   <si>
     <t>testAddMajorFailWithIdInvalid</t>
@@ -71,7 +71,7 @@
     <t>TC_CM_04</t>
   </si>
   <si>
-    <t>5740 ms</t>
+    <t>4947 ms</t>
   </si>
   <si>
     <t>testAddMajorFailWithEmpty</t>
@@ -80,7 +80,7 @@
     <t>TC_CM_05</t>
   </si>
   <si>
-    <t>8916 ms</t>
+    <t>5865 ms</t>
   </si>
   <si>
     <t>testAddMajorFailWithInfoBoundary</t>
@@ -89,7 +89,7 @@
     <t>TC_CM_06</t>
   </si>
   <si>
-    <t>7849 ms</t>
+    <t>6080 ms</t>
   </si>
 </sst>
 </file>
